--- a/Reinfection_Augments_Heterogeneity/Public/Results/Supplementary/TableS1.xlsx
+++ b/Reinfection_Augments_Heterogeneity/Public/Results/Supplementary/TableS1.xlsx
@@ -411,13 +411,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>-3.076266988844058</v>
+        <v>-3.07133672929243</v>
       </c>
       <c r="E2">
-        <v>0.007901796385993996</v>
+        <v>0.008888770723688769</v>
       </c>
       <c r="F2">
-        <v>-389.3123586804601</v>
+        <v>-345.5299753775008</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -440,16 +440,16 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.01434466579136773</v>
+        <v>0.009104830967596062</v>
       </c>
       <c r="E3">
-        <v>0.01261437968991311</v>
+        <v>0.01333563660543443</v>
       </c>
       <c r="F3">
-        <v>1.137167751723711</v>
+        <v>0.6827443816132281</v>
       </c>
       <c r="G3">
-        <v>0.2554681652582663</v>
+        <v>0.4947683800009502</v>
       </c>
     </row>
     <row r="4">
@@ -469,16 +469,16 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00477515285558764</v>
+        <v>0.0004953303044605932</v>
       </c>
       <c r="E4">
-        <v>0.0114846327540356</v>
+        <v>0.01235612232990765</v>
       </c>
       <c r="F4">
-        <v>0.4157862909381836</v>
+        <v>0.04008784400439771</v>
       </c>
       <c r="G4">
-        <v>0.6775663913030427</v>
+        <v>0.9680230930916778</v>
       </c>
     </row>
     <row r="5">
@@ -498,16 +498,16 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.04284637704205283</v>
+        <v>-0.04016060602024529</v>
       </c>
       <c r="E5">
-        <v>0.009088490552559871</v>
+        <v>0.0106790636086631</v>
       </c>
       <c r="F5">
-        <v>-4.714355678125747</v>
+        <v>-3.760686094955561</v>
       </c>
       <c r="G5">
-        <v>2.424767930801482E-06</v>
+        <v>0.0001694479602290389</v>
       </c>
     </row>
     <row r="6">
@@ -527,16 +527,16 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.02349643612450475</v>
+        <v>-0.02951758440998267</v>
       </c>
       <c r="E6">
-        <v>0.01221266926053316</v>
+        <v>0.01210416721373845</v>
       </c>
       <c r="F6">
-        <v>-1.923939445444294</v>
+        <v>-2.438629927094834</v>
       </c>
       <c r="G6">
-        <v>0.05436217416647508</v>
+        <v>0.0147430577622494</v>
       </c>
     </row>
     <row r="7">
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.3009796753929092</v>
+        <v>0.279134338618734</v>
       </c>
       <c r="E7">
-        <v>0.05037171567283672</v>
+        <v>0.0491229378750106</v>
       </c>
       <c r="F7">
-        <v>5.975172204730253</v>
+        <v>5.682362470440371</v>
       </c>
       <c r="G7">
-        <v>2.298472597082224E-09</v>
+        <v>1.328467321388792E-08</v>
       </c>
     </row>
     <row r="8">
@@ -585,16 +585,16 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.7580076814470365</v>
+        <v>0.7671367102902855</v>
       </c>
       <c r="E8">
-        <v>0.04298747477927144</v>
+        <v>0.04354116469359165</v>
       </c>
       <c r="F8">
-        <v>17.6332218940329</v>
+        <v>17.61865388050109</v>
       </c>
       <c r="G8">
-        <v>1.369365449228675E-69</v>
+        <v>1.771707252895494E-69</v>
       </c>
     </row>
     <row r="9">
@@ -614,16 +614,16 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.05103670841076696</v>
+        <v>0.05137607758440808</v>
       </c>
       <c r="E9">
-        <v>0.02506225360209987</v>
+        <v>0.02437359019492315</v>
       </c>
       <c r="F9">
-        <v>2.036397413458892</v>
+        <v>2.107858430930268</v>
       </c>
       <c r="G9">
-        <v>0.04171046496662752</v>
+        <v>0.03504323683147771</v>
       </c>
     </row>
     <row r="10">
@@ -643,16 +643,16 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.2416145648397671</v>
+        <v>0.2506113615023259</v>
       </c>
       <c r="E10">
-        <v>0.03408476627422061</v>
+        <v>0.03476695879287198</v>
       </c>
       <c r="F10">
-        <v>7.088637865253836</v>
+        <v>7.208319916486538</v>
       </c>
       <c r="G10">
-        <v>1.354384157872681E-12</v>
+        <v>5.664642119769752E-13</v>
       </c>
     </row>
   </sheetData>
@@ -699,16 +699,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>5.925389403678225</v>
+        <v>5.686886526850138</v>
       </c>
       <c r="C2">
-        <v>0.2262941184984142</v>
+        <v>0.2276042334437799</v>
       </c>
       <c r="D2">
-        <v>26.1844604844193</v>
+        <v>24.9858556706277</v>
       </c>
       <c r="E2">
-        <v>3.994637733097015E-151</v>
+        <v>8.710719072779208E-138</v>
       </c>
     </row>
     <row r="3">
@@ -718,16 +718,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-0.570809050134746</v>
+        <v>-0.255148132125104</v>
       </c>
       <c r="C3">
-        <v>0.3256664771852626</v>
+        <v>0.3517499839013618</v>
       </c>
       <c r="D3">
-        <v>-1.752741194206576</v>
+        <v>-0.7253678572922208</v>
       </c>
       <c r="E3">
-        <v>0.0796464412584587</v>
+        <v>0.4682263865802921</v>
       </c>
     </row>
     <row r="4">
@@ -737,16 +737,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2637203568349231</v>
+        <v>0.08403130710121763</v>
       </c>
       <c r="C4">
-        <v>0.3389845045427571</v>
+        <v>0.3915025487965059</v>
       </c>
       <c r="D4">
-        <v>-0.7779717164082328</v>
+        <v>0.2146379566609034</v>
       </c>
       <c r="E4">
-        <v>0.4365856873621443</v>
+        <v>0.8300495984142933</v>
       </c>
     </row>
     <row r="5">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.313880969308691</v>
+        <v>0.7952463743920735</v>
       </c>
       <c r="C5">
-        <v>0.4934017621532525</v>
+        <v>0.4228280503197422</v>
       </c>
       <c r="D5">
-        <v>2.66290287163708</v>
+        <v>1.880779607196611</v>
       </c>
       <c r="E5">
-        <v>0.007746977185533919</v>
+        <v>0.06000190532963712</v>
       </c>
     </row>
     <row r="6">
@@ -775,16 +775,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.44962242348343</v>
+        <v>-0.1478251103266913</v>
       </c>
       <c r="C6">
-        <v>0.3309094287644039</v>
+        <v>0.3329141926534831</v>
       </c>
       <c r="D6">
-        <v>-1.358747694685803</v>
+        <v>-0.4440336687014016</v>
       </c>
       <c r="E6">
-        <v>0.1742265529427592</v>
+        <v>0.6570182419462679</v>
       </c>
     </row>
     <row r="7">
@@ -794,16 +794,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>-4.532134696333958</v>
+        <v>-4.004106596938425</v>
       </c>
       <c r="C7">
-        <v>0.6041760276957771</v>
+        <v>0.5524442285541209</v>
       </c>
       <c r="D7">
-        <v>-7.501348098200348</v>
+        <v>-7.247983398103611</v>
       </c>
       <c r="E7">
-        <v>6.316479991873953E-14</v>
+        <v>4.230224478687002E-13</v>
       </c>
     </row>
     <row r="8">
@@ -813,16 +813,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>-4.56860692333193</v>
+        <v>-4.112147607201339</v>
       </c>
       <c r="C8">
-        <v>0.6187725605333436</v>
+        <v>0.5817061880301106</v>
       </c>
       <c r="D8">
-        <v>-7.383337941478972</v>
+        <v>-7.069114428929685</v>
       </c>
       <c r="E8">
-        <v>1.543695370045463E-13</v>
+        <v>1.559255349090969E-12</v>
       </c>
     </row>
     <row r="9">
@@ -832,16 +832,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.957736644635008</v>
+        <v>-1.245314595300364</v>
       </c>
       <c r="C9">
-        <v>0.4491263194091313</v>
+        <v>0.4666540680729226</v>
       </c>
       <c r="D9">
-        <v>-2.132443820916579</v>
+        <v>-2.668603319891691</v>
       </c>
       <c r="E9">
-        <v>0.03297037821095014</v>
+        <v>0.007616734799411521</v>
       </c>
     </row>
     <row r="10">
@@ -851,16 +851,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>-2.2198557492133</v>
+        <v>-2.626389514248428</v>
       </c>
       <c r="C10">
-        <v>0.4606930346555927</v>
+        <v>0.4980639941584775</v>
       </c>
       <c r="D10">
-        <v>-4.818513809033019</v>
+        <v>-5.273196908533696</v>
       </c>
       <c r="E10">
-        <v>1.446315171350166E-06</v>
+        <v>1.340675833521367E-07</v>
       </c>
     </row>
   </sheetData>
@@ -922,7 +922,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.01416896963559799</v>
+        <v>0.02363628153138595</v>
       </c>
     </row>
   </sheetData>
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>-0.01434466579136773</v>
+        <v>-0.009104830967596062</v>
       </c>
       <c r="D2">
-        <v>0.01261437968991311</v>
+        <v>0.01333563660543443</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="F2">
-        <v>-1.137167751723711</v>
+        <v>-0.6827443816132281</v>
       </c>
       <c r="G2">
-        <v>0.4911359281515456</v>
+        <v>0.7735656898842453</v>
       </c>
     </row>
     <row r="3">
@@ -1013,10 +1013,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.00477515285558764</v>
+        <v>-0.0004953303044605932</v>
       </c>
       <c r="D3">
-        <v>0.0114846327540356</v>
+        <v>0.01235612232990765</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="F3">
-        <v>-0.4157862909381836</v>
+        <v>-0.04008784400439771</v>
       </c>
       <c r="G3">
-        <v>0.9091201447638275</v>
+        <v>0.9991143904307476</v>
       </c>
     </row>
     <row r="4">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.009569512935780089</v>
+        <v>0.008609500663135469</v>
       </c>
       <c r="D4">
-        <v>0.01288533516952414</v>
+        <v>0.01312577478322863</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="F4">
-        <v>0.7426669783812458</v>
+        <v>0.6559232354143545</v>
       </c>
       <c r="G4">
-        <v>0.7380558574138782</v>
+        <v>0.7890018376889508</v>
       </c>
     </row>
     <row r="5">
@@ -1071,10 +1071,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>-0.3153243411842769</v>
+        <v>-0.2882391695863301</v>
       </c>
       <c r="D5">
-        <v>0.04893860761456906</v>
+        <v>0.04775360346397708</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="F5">
-        <v>-6.443263438708964</v>
+        <v>-6.035966894179269</v>
       </c>
       <c r="G5">
-        <v>3.507665269353311E-10</v>
+        <v>4.738698100581473E-09</v>
       </c>
     </row>
     <row r="6">
@@ -1100,10 +1100,10 @@
         </is>
       </c>
       <c r="C6">
-        <v>-0.7627828343026241</v>
+        <v>-0.7676320405947461</v>
       </c>
       <c r="D6">
-        <v>0.04162407033596514</v>
+        <v>0.04229056212568187</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F6">
-        <v>-18.32552242358538</v>
+        <v>-18.1513794570393</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.4474584931183472</v>
+        <v>-0.479392871008416</v>
       </c>
       <c r="D7">
-        <v>0.06379952036364171</v>
+        <v>0.06288192271416888</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="F7">
-        <v>-7.013508731224668</v>
+        <v>-7.623699313195407</v>
       </c>
       <c r="G7">
-        <v>6.995182211255724E-12</v>
+        <v>9.259260025373806E-14</v>
       </c>
     </row>
     <row r="8">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="C8">
-        <v>-0.06538137420213469</v>
+        <v>-0.06048090855200414</v>
       </c>
       <c r="D8">
-        <v>0.02204000525048458</v>
+        <v>0.02147749918196171</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -1169,10 +1169,10 @@
         </is>
       </c>
       <c r="F8">
-        <v>-2.966486326072776</v>
+        <v>-2.816012611133059</v>
       </c>
       <c r="G8">
-        <v>0.008465668902225332</v>
+        <v>0.01348440155036801</v>
       </c>
     </row>
     <row r="9">
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.2463897176953548</v>
+        <v>-0.2511066918067865</v>
       </c>
       <c r="D9">
-        <v>0.03234938576407405</v>
+        <v>0.0331879714057009</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1198,10 +1198,10 @@
         </is>
       </c>
       <c r="F9">
-        <v>-7.616519197374853</v>
+        <v>-7.566195858649328</v>
       </c>
       <c r="G9">
-        <v>9.670042544485113E-14</v>
+        <v>1.344480082821065E-13</v>
       </c>
     </row>
     <row r="10">
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>-0.1810083434932201</v>
+        <v>-0.1906257832547823</v>
       </c>
       <c r="D10">
-        <v>0.03662093708616135</v>
+        <v>0.0371780274773774</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1227,10 +1227,10 @@
         </is>
       </c>
       <c r="F10">
-        <v>-4.94275564460149</v>
+        <v>-5.127377544996892</v>
       </c>
       <c r="G10">
-        <v>2.303401201109168E-06</v>
+        <v>8.794144417123562E-07</v>
       </c>
     </row>
   </sheetData>
